--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -953,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2670,10 +2670,10 @@
         <v>0.590445</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3014,10 +3014,10 @@
         <v>0.646047</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
@@ -3060,7 +3060,7 @@
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -4261,10 +4261,10 @@
         <v>0.948531</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -4350,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -5597,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
         <v>1</v>
@@ -7059,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J154" t="n">
         <v>1</v>
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J190" t="n">
         <v>1</v>
@@ -8650,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J191" t="n">
         <v>1</v>
@@ -9381,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -9854,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
         <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J233" t="n">
         <v>1</v>
@@ -11055,10 +11055,10 @@
         <v>0.861781</v>
       </c>
       <c r="H247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I247" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J247" t="n">
         <v>1</v>
@@ -11144,7 +11144,7 @@
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J249" t="n">
         <v>1</v>
@@ -11660,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="I261" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -13165,7 +13165,7 @@
         <v>0</v>
       </c>
       <c r="I296" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J296" t="n">
         <v>1</v>
@@ -13463,10 +13463,10 @@
         <v>0.499185</v>
       </c>
       <c r="H303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J303" t="n">
         <v>1</v>
@@ -13509,7 +13509,7 @@
         <v>1</v>
       </c>
       <c r="I304" t="n">
-        <v>0.666667</v>
+        <v>1</v>
       </c>
       <c r="J304" t="n">
         <v>1</v>

--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.195669</v>
+        <v>0.116146</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.373331</v>
+        <v>0.146356</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.180882</v>
+        <v>0.14444</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.966853</v>
+        <v>0.9995849999999999</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.22494</v>
+        <v>0.186635</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.96097</v>
+        <v>0.996515</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.178518</v>
+        <v>0.08686199999999999</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.202126</v>
+        <v>0.172247</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.228014</v>
+        <v>0.230138</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.095388</v>
+        <v>0.101245</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.178156</v>
+        <v>0.151113</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.214535</v>
+        <v>0.178876</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.26838</v>
+        <v>0.447006</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.171088</v>
+        <v>0.09805999999999999</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.603167</v>
+        <v>0.609702</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.213155</v>
+        <v>0.15371</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.297959</v>
+        <v>0.328722</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.561379</v>
+        <v>0.904335</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5717,10 +5717,10 @@
         <v>0.1139</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.370335</v>
+        <v>0.566811</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.266867</v>
+        <v>0.100339</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.178939</v>
+        <v>0.065707</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.190286</v>
+        <v>0.14252</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.149319</v>
+        <v>0.098527</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.212656</v>
+        <v>0.169021</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6369359999999999</v>
+        <v>0.840663</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.358882</v>
+        <v>0.296492</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.285739</v>
+        <v>0.142234</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.247246</v>
+        <v>0.149507</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.189995</v>
+        <v>0.09728100000000001</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.293926</v>
+        <v>0.230628</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.214347</v>
+        <v>0.096416</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.161029</v>
+        <v>0.08133799999999999</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.188168</v>
+        <v>0.09217400000000001</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.168191</v>
+        <v>0.101157</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.175088</v>
+        <v>0.109809</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.118104</v>
+        <v>0.069469</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.310336</v>
+        <v>0.213059</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.147281</v>
+        <v>0.136967</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.354522</v>
+        <v>0.2284</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.239333</v>
+        <v>0.198977</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.23479</v>
+        <v>0.143279</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.323789</v>
+        <v>0.2825</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.339986</v>
+        <v>0.220078</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.215786</v>
+        <v>0.099414</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.489079</v>
+        <v>0.427192</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.240061</v>
+        <v>0.102263</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.423185</v>
+        <v>0.4963</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.999401</v>
+        <v>0.999994</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.248942</v>
+        <v>0.356334</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.192908</v>
+        <v>0.054214</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.235497</v>
+        <v>0.18855</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.350823</v>
+        <v>0.288339</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.325115</v>
+        <v>0.324981</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.325638</v>
+        <v>0.260296</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.165393</v>
+        <v>0.042896</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.204722</v>
+        <v>0.142306</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.179232</v>
+        <v>0.098245</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.14976</v>
+        <v>0.127211</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.368541</v>
+        <v>0.336844</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.180935</v>
+        <v>0.056208</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.152944</v>
+        <v>0.069753</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.279091</v>
+        <v>0.406068</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.270397</v>
+        <v>0.11485</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.311769</v>
+        <v>0.167112</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.204108</v>
+        <v>0.115226</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.192017</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.135064</v>
+        <v>0.142742</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.271076</v>
+        <v>0.26641</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.128561</v>
+        <v>0.096013</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.164652</v>
+        <v>0.077408</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.257691</v>
+        <v>0.10258</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.362771</v>
+        <v>0.392071</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.163758</v>
+        <v>0.061503</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.22372</v>
+        <v>0.121311</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.134367</v>
+        <v>0.111457</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.083783</v>
+        <v>0.025825</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.209257</v>
+        <v>0.180361</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.240226</v>
+        <v>0.173123</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.117852</v>
+        <v>0.069214</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.187201</v>
+        <v>0.090214</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.187408</v>
+        <v>0.106995</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.17604</v>
+        <v>0.100904</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.185068</v>
+        <v>0.07228</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.320936</v>
+        <v>0.311828</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.216039</v>
+        <v>0.081964</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>0.270521</v>
+        <v>0.213547</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8641,10 +8641,10 @@
         <v>0.001553</v>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.531739</v>
+        <v>0.33363</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8684,10 +8684,10 @@
         <v>0.004377</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" t="n">
-        <v>0.36402</v>
+        <v>0.559725</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8727,10 +8727,10 @@
         <v>0.000746</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.586763</v>
+        <v>0.41673</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.176758</v>
+        <v>0.072187</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.254285</v>
+        <v>0.189764</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.432173</v>
+        <v>0.386679</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.85465</v>
+        <v>0.963121</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.992384</v>
+        <v>0.999689</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.534278</v>
+        <v>0.738801</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>1</v>
       </c>
       <c r="G200" t="n">
-        <v>0.84634</v>
+        <v>0.925553</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.292022</v>
+        <v>0.10432</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.092199</v>
+        <v>0.057613</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.650284</v>
+        <v>0.868838</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.851534</v>
+        <v>0.75814</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.200999</v>
+        <v>0.238992</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.6898030000000001</v>
+        <v>0.837198</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>0.286869</v>
+        <v>0.234523</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.216503</v>
+        <v>0.239086</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.274599</v>
+        <v>0.311143</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9458,10 +9458,10 @@
         <v>0.54997</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.447797</v>
+        <v>0.656637</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.149088</v>
+        <v>0.1433</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.132547</v>
+        <v>0.167346</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.204372</v>
+        <v>0.237153</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.184417</v>
+        <v>0.178805</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.160469</v>
+        <v>0.206777</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>0.284366</v>
+        <v>0.31175</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.128398</v>
+        <v>0.095814</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9805,7 +9805,7 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.360771</v>
+        <v>0.331763</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9845,10 +9845,10 @@
         <v>0.000358</v>
       </c>
       <c r="F219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.531228</v>
+        <v>0.492988</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.145422</v>
+        <v>0.18051</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9931,10 +9931,10 @@
         <v>0.126322</v>
       </c>
       <c r="F221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G221" t="n">
-        <v>0.391274</v>
+        <v>0.537265</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="G222" t="n">
-        <v>0.545797</v>
+        <v>0.575226</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.271145</v>
+        <v>0.307842</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.179496</v>
+        <v>0.160206</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.229785</v>
+        <v>0.217595</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.146607</v>
+        <v>0.13441</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.252575</v>
+        <v>0.297002</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.147689</v>
+        <v>0.196317</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.15762</v>
+        <v>0.118791</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.142387</v>
+        <v>0.140569</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10361,10 +10361,10 @@
         <v>0.010238</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.476772</v>
+        <v>0.6246350000000001</v>
       </c>
       <c r="H231" t="n">
         <v>1</v>
@@ -10404,10 +10404,10 @@
         <v>1.2e-05</v>
       </c>
       <c r="F232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232" t="n">
-        <v>0.338847</v>
+        <v>0.509784</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0.998489</v>
+        <v>0.998178</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.518825</v>
+        <v>0.454699</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>0.258176</v>
+        <v>0.424925</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.186308</v>
+        <v>0.181494</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.157465</v>
+        <v>0.143005</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.130865</v>
+        <v>0.133958</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.16169</v>
+        <v>0.170806</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.129577</v>
+        <v>0.172497</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.194539</v>
+        <v>0.252702</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.146963</v>
+        <v>0.146151</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.208078</v>
+        <v>0.200814</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>1</v>
       </c>
       <c r="G244" t="n">
-        <v>0.784618</v>
+        <v>0.7374810000000001</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10963,10 +10963,10 @@
         <v>0.008181000000000001</v>
       </c>
       <c r="F245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.470282</v>
+        <v>0.717575</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.831921</v>
+        <v>0.92779</v>
       </c>
       <c r="H246" t="n">
         <v>1</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.861781</v>
+        <v>0.98289</v>
       </c>
       <c r="H247" t="n">
         <v>1</v>
@@ -11095,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.539994</v>
+        <v>0.701257</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.980542</v>
+        <v>0.990873</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.177435</v>
+        <v>0.203061</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.2493</v>
+        <v>0.250573</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.773019</v>
+        <v>0.87375</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.283756</v>
+        <v>0.202288</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.136007</v>
+        <v>0.160908</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="G255" t="n">
-        <v>0.552872</v>
+        <v>0.731912</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.873892</v>
+        <v>0.921125</v>
       </c>
       <c r="H256" t="n">
         <v>1</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.933242</v>
+        <v>0.934598</v>
       </c>
       <c r="H257" t="n">
         <v>1</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.891805</v>
+        <v>0.949527</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.940916</v>
+        <v>0.98817</v>
       </c>
       <c r="H259" t="n">
         <v>1</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.171241</v>
+        <v>0.143836</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>0.422546</v>
+        <v>0.461509</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="G262" t="n">
-        <v>0.619628</v>
+        <v>0.779155</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.110002</v>
+        <v>0.094088</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.937099</v>
+        <v>0.944653</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.200227</v>
+        <v>0.174306</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.226508</v>
+        <v>0.298948</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.908963</v>
+        <v>0.884442</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0.738684</v>
+        <v>0.945699</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.181462</v>
+        <v>0.141538</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.358981</v>
+        <v>0.282975</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.217943</v>
+        <v>0.136588</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0.333116</v>
+        <v>0.392074</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>0.382259</v>
+        <v>0.36846</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>0.599949</v>
+        <v>0.604943</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.351557</v>
+        <v>0.366068</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>0.579464</v>
+        <v>0.781909</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.21625</v>
+        <v>0.244293</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0.448961</v>
+        <v>0.46326</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.464376</v>
+        <v>0.267779</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.141123</v>
+        <v>0.151738</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.146335</v>
+        <v>0.187481</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.129663</v>
+        <v>0.092929</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.239352</v>
+        <v>0.16648</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.225739</v>
+        <v>0.158043</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.235909</v>
+        <v>0.220286</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0.424408</v>
+        <v>0.320313</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
         <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0.627306</v>
+        <v>0.619876</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.390933</v>
+        <v>0.27569</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.162441</v>
+        <v>0.220718</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.228765</v>
+        <v>0.191815</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.268781</v>
+        <v>0.17491</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.328317</v>
+        <v>0.309376</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.234734</v>
+        <v>0.246143</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.140699</v>
+        <v>0.162655</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.174092</v>
+        <v>0.236734</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.9962259999999999</v>
+        <v>0.9990329999999999</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -13202,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="G297" t="n">
-        <v>0.349698</v>
+        <v>0.311642</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.178008</v>
+        <v>0.17459</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>0.245168</v>
+        <v>0.421395</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>0.310071</v>
+        <v>0.309474</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.176836</v>
+        <v>0.141603</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13414,10 +13414,10 @@
         <v>4e-06</v>
       </c>
       <c r="F302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0.489907</v>
+        <v>0.515423</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13457,10 +13457,10 @@
         <v>0.962112</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.499185</v>
+        <v>0.676362</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.755322</v>
+        <v>0.945508</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.206472</v>
+        <v>0.112768</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.308198</v>
+        <v>0.347514</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0.214834</v>
+        <v>0.201151</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.305957</v>
+        <v>0.371982</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.541055</v>
+        <v>0.808663</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.104496</v>
+        <v>0.12473</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.323283</v>
+        <v>0.25155</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.137621</v>
+        <v>0.189169</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.187925</v>
+        <v>0.225827</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
